--- a/templates/forms/LTCI_Address_Change_Notice.xlsx
+++ b/templates/forms/LTCI_Address_Change_Notice.xlsx
@@ -8,22 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CareManagementTool\templates\forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C0B35F-AA01-492F-BAE6-1AB3DF5DB67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{068FC092-968A-472B-BB72-C6F1E9AA36B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15885" yWindow="4680" windowWidth="12735" windowHeight="7980" xr2:uid="{D73D3C2D-752B-46D9-A1D6-D07A1C0CE744}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D73D3C2D-752B-46D9-A1D6-D07A1C0CE744}"/>
   </bookViews>
   <sheets>
     <sheet name="介護保険被保険者証等の送付先変更届" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">介護保険被保険者証等の送付先変更届!$B$2:$O$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">介護保険被保険者証等の送付先変更届!$B$2:$O$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>被保険者との関係</t>
     <rPh sb="0" eb="4">
@@ -124,10 +124,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>（　　　　　　　　）　　　　－</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>送付先</t>
     <rPh sb="0" eb="2">
       <t>ソウフ</t>
@@ -139,10 +135,6 @@
   </si>
   <si>
     <t>　　　　</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>〒　　　　　－</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -583,26 +575,11 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>　　　令和　　年　　月　　日</t>
-    <rPh sb="3" eb="4">
-      <t>レイ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>ワ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ネン</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ガツ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>ニチ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t xml:space="preserve"> ※自署でない場合は、記名と押印が必要です。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>〒</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1044,7 +1021,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="57">
     <border>
       <left/>
       <right/>
@@ -1313,19 +1290,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -1662,6 +1626,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1742,56 +1783,56 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="43" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="42" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="46" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="47" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="46" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="47" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="49" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="50" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="48" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="49" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="45" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="44" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1807,22 +1848,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
@@ -1861,25 +1890,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1900,130 +1911,181 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2082,137 +2144,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>295274</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="" fLocksText="0">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="円/楕円 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B319B413-B416-6F49-FBA9-8C51A44B2928}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="676275" y="6276975"/>
-          <a:ext cx="323850" cy="247649"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="15875">
-          <a:prstDash val="sysDot"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>276225</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>571500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="" fLocksText="0">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="円/楕円 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4169FFC6-C6E3-6C80-05EF-6DFA6C702B27}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="666750" y="7096125"/>
-          <a:ext cx="361950" cy="295275"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="15875">
-          <a:prstDash val="sysDot"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:endParaRPr lang="ja-JP" altLang="en-US"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2502,7 +2433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB932479-A3F9-4035-98A5-B6AB03054D4C}">
-  <dimension ref="B1:Q38"/>
+  <dimension ref="B1:Q41"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="0.875" customWidth="1"/>
@@ -2517,51 +2448,49 @@
   <sheetData>
     <row r="1" spans="2:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="2" spans="2:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.15">
-      <c r="B2" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="50"/>
-      <c r="N2" s="50"/>
+      <c r="B2" s="53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
     </row>
     <row r="3" spans="2:14" s="1" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
     </row>
     <row r="4" spans="2:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="54"/>
     </row>
     <row r="5" spans="2:14" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="2" t="s">
@@ -2582,462 +2511,501 @@
     </row>
     <row r="6" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" s="14"/>
+        <v>19</v>
+      </c>
+      <c r="K7" s="10"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
     <row r="8" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" s="14"/>
+        <v>13</v>
+      </c>
+      <c r="K8" s="10"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
     <row r="9" spans="2:14" s="2" customFormat="1" ht="9" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="K9" s="14"/>
+      <c r="K9" s="10"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="2:14" s="2" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="53" t="s">
+    <row r="10" spans="2:14" s="2" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="58" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="54"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="2:14" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="56" t="s">
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="65"/>
+      <c r="G10" s="65"/>
+      <c r="H10" s="65"/>
+      <c r="I10" s="65"/>
+      <c r="J10" s="65"/>
+      <c r="K10" s="65"/>
+      <c r="L10" s="65"/>
+      <c r="M10" s="65"/>
+      <c r="N10" s="66"/>
+    </row>
+    <row r="11" spans="2:14" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="63"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="N11" s="32"/>
+    </row>
+    <row r="12" spans="2:14" s="2" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="57"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="20"/>
-    </row>
-    <row r="12" spans="2:14" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="59"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="48"/>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="48"/>
-      <c r="M12" s="48"/>
-      <c r="N12" s="52"/>
-    </row>
-    <row r="13" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="53" t="s">
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="16"/>
+    </row>
+    <row r="13" spans="2:14" s="2" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="60"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="55"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="57"/>
+    </row>
+    <row r="14" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="54"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="37"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="39"/>
-    </row>
-    <row r="14" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="53" t="s">
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="68"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="69"/>
+      <c r="L14" s="69"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="70"/>
+    </row>
+    <row r="15" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B15" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="40" t="s">
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="52"/>
+    </row>
+    <row r="16" spans="2:14" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="41"/>
+      <c r="D16" s="42"/>
+      <c r="E16" s="76" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="77"/>
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="78"/>
+    </row>
+    <row r="17" spans="2:14" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="2:14" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="45"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+      <c r="J18" s="27"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="27"/>
+      <c r="M18" s="27"/>
+      <c r="N18" s="35"/>
+    </row>
+    <row r="19" spans="2:14" s="2" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B19" s="43"/>
+      <c r="C19" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="50"/>
+    </row>
+    <row r="20" spans="2:14" s="2" customFormat="1" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="79"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="81"/>
+    </row>
+    <row r="21" spans="2:14" s="2" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="17"/>
+    </row>
+    <row r="22" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="74" t="s">
         <v>10</v>
       </c>
-      <c r="F14" s="40"/>
-      <c r="G14" s="40"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="40"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="41"/>
-    </row>
-    <row r="15" spans="2:14" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="65" t="s">
+      <c r="C23" s="18">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="15"/>
+    </row>
+    <row r="24" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="74"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="65"/>
+      <c r="F24" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G24" s="82"/>
+      <c r="H24" s="82"/>
+      <c r="I24" s="82"/>
+      <c r="J24" s="82"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+      <c r="N24" s="25"/>
+    </row>
+    <row r="25" spans="2:14" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="74"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="83"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="84"/>
+    </row>
+    <row r="26" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="74"/>
+      <c r="C26" s="31">
+        <v>2</v>
+      </c>
+      <c r="D26" s="72"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="83"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="84"/>
+    </row>
+    <row r="27" spans="2:14" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="74"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="63"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="61"/>
+      <c r="K27" s="61"/>
+      <c r="L27" s="61"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="75"/>
+    </row>
+    <row r="28" spans="2:14" s="2" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="74"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="49"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="52"/>
+    </row>
+    <row r="29" spans="2:14" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="11"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+    </row>
+    <row r="30" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="C30" s="21"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+    </row>
+    <row r="31" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="21"/>
+    </row>
+    <row r="32" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="21"/>
+    </row>
+    <row r="33" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="21"/>
+      <c r="M33" s="21"/>
+      <c r="N33" s="21"/>
+    </row>
+    <row r="34" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="K34" s="10"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+    </row>
+    <row r="35" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="K35" s="10"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+    </row>
+    <row r="36" spans="2:14" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+    </row>
+    <row r="37" spans="2:14" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="3"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3"/>
+    </row>
+    <row r="38" spans="2:14" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="8"/>
+    </row>
+    <row r="39" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C39" s="36"/>
+      <c r="D39" s="37"/>
+      <c r="E39" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="25"/>
-    </row>
-    <row r="16" spans="2:14" s="2" customFormat="1" ht="10.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:14" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>3</v>
-      </c>
-      <c r="D17" s="70"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="10"/>
-    </row>
-    <row r="18" spans="2:14" s="2" customFormat="1" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="68"/>
-      <c r="C18" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="72"/>
-      <c r="I18" s="72"/>
-      <c r="J18" s="72"/>
-      <c r="K18" s="72"/>
-      <c r="L18" s="72"/>
-      <c r="M18" s="72"/>
-      <c r="N18" s="75"/>
-    </row>
-    <row r="19" spans="2:14" s="2" customFormat="1" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="29"/>
-    </row>
-    <row r="20" spans="2:14" s="2" customFormat="1" ht="9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="21"/>
-    </row>
-    <row r="21" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="33" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="49" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="22">
-        <v>1</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
-      <c r="J22" s="18"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="18"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="19"/>
-    </row>
-    <row r="23" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="49"/>
-      <c r="C23" s="42">
-        <v>2</v>
-      </c>
-      <c r="D23" s="45" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="46"/>
-      <c r="F23" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="35"/>
-    </row>
-    <row r="24" spans="2:14" s="2" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="49"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="47"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="62"/>
-      <c r="G24" s="60"/>
-      <c r="H24" s="60"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="60"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="60"/>
-      <c r="M24" s="60"/>
-      <c r="N24" s="61"/>
-    </row>
-    <row r="25" spans="2:14" s="2" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="49"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="74"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
-      <c r="J25" s="74"/>
-      <c r="K25" s="74"/>
-      <c r="L25" s="74"/>
-      <c r="M25" s="74"/>
-      <c r="N25" s="77"/>
-    </row>
-    <row r="26" spans="2:14" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="15"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-    </row>
-    <row r="27" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-    </row>
-    <row r="28" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="31"/>
-    </row>
-    <row r="29" spans="2:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" s="31"/>
-    </row>
-    <row r="30" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="31"/>
-      <c r="F30" s="31"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
-    </row>
-    <row r="31" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="31" t="s">
-        <v>32</v>
-      </c>
-      <c r="K31" s="14"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-    </row>
-    <row r="32" spans="2:14" s="2" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" s="14"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-    </row>
-    <row r="33" spans="2:14" s="1" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="16"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="17"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="17"/>
-      <c r="J33" s="17"/>
-      <c r="K33" s="17"/>
-      <c r="L33" s="17"/>
-      <c r="M33" s="17"/>
-      <c r="N33" s="17"/>
-    </row>
-    <row r="34" spans="2:14" s="1" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="2" t="s">
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="6"/>
+    </row>
+    <row r="40" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E40" t="s">
         <v>26</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" s="2" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="63"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="11"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="12"/>
-    </row>
-    <row r="36" spans="2:14" s="2" customFormat="1" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="B36" s="63" t="s">
-        <v>0</v>
-      </c>
-      <c r="C36" s="63"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="7"/>
-      <c r="J36" s="7"/>
-      <c r="K36" s="7"/>
-      <c r="L36" s="7"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="8"/>
-    </row>
-    <row r="37" spans="2:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E37" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="38" spans="2:14" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
+    </row>
+    <row r="41" spans="2:14" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B35:D35"/>
+  <mergeCells count="27">
+    <mergeCell ref="E14:N14"/>
+    <mergeCell ref="E15:N15"/>
+    <mergeCell ref="D24:E27"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="F27:N27"/>
     <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="E18:N18"/>
-    <mergeCell ref="F25:N25"/>
+    <mergeCell ref="E16:N16"/>
+    <mergeCell ref="C20:N20"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="F25:N26"/>
     <mergeCell ref="B2:N2"/>
     <mergeCell ref="J4:N4"/>
-    <mergeCell ref="E12:N12"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D12"/>
     <mergeCell ref="E13:N13"/>
-    <mergeCell ref="E14:N14"/>
-    <mergeCell ref="C23:C25"/>
-    <mergeCell ref="D23:E24"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="F24:N24"/>
-    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B12:D13"/>
+    <mergeCell ref="B10:D11"/>
+    <mergeCell ref="E10:N10"/>
+    <mergeCell ref="F12:I12"/>
+    <mergeCell ref="B38:D38"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B39:D39"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="E19:N19"/>
+    <mergeCell ref="F28:N28"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.86614173228346458" right="0.6692913385826772" top="0.55118110236220474" bottom="0.51181102362204722" header="0.51181102362204722" footer="0.51181102362204722"/>
   <pageSetup paperSize="9" orientation="portrait" blackAndWhite="1" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>